--- a/diseases/d064/1995-1999.xlsx
+++ b/diseases/d064/1995-1999.xlsx
@@ -761,11 +761,6 @@
       <c r="O2" t="n">
         <v>0</v>
       </c>
-      <c r="S2" t="inlineStr">
-        <is>
-          <t>missing_population</t>
-        </is>
-      </c>
       <c r="U2" t="inlineStr">
         <is>
           <t>SER_IS_HISTORY_SMALLPOX_ANNUAL</t>
@@ -783,12 +778,7 @@
       </c>
       <c r="AP2" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ2" t="inlineStr">
-        <is>
-          <t>parity</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS2" t="inlineStr">
@@ -799,11 +789,6 @@
       <c r="AT2" t="n">
         <v>1</v>
       </c>
-      <c r="AU2" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series.</t>
-        </is>
-      </c>
       <c r="AV2" t="inlineStr">
         <is>
           <t>is_doh_annual</t>
@@ -826,22 +811,22 @@
       </c>
       <c r="AZ2" t="inlineStr">
         <is>
-          <t>is_doh_annual; is_doh_sti; is_doh_respiratory; is_doh_history; is_doh_legacy_icd</t>
+          <t>is_doh_annual; is_doh_sti; is_doh_respiratory; is_doh_history; is_doh_legacy_icd; ecdc_atlas_annual</t>
         </is>
       </c>
       <c r="BA2" t="inlineStr">
         <is>
-          <t>Iceland Directorate of Health Annual Dashboard; Iceland Directorate of Health STI Dashboard; Iceland Directorate of Health Respiratory Dashboard; Iceland Directorate of Health Historical Registry; Iceland Directorate of Health Legacy ICD Monthly</t>
+          <t>Iceland Directorate of Health Annual Dashboard; Iceland Directorate of Health STI Dashboard; Iceland Directorate of Health Respiratory Dashboard; Iceland Directorate of Health Historical Registry; Iceland Directorate of Health Legacy ICD Monthly; ECDC Surveillance Atlas — Iceland Annual Baseline</t>
         </is>
       </c>
       <c r="BB2" t="inlineStr">
         <is>
-          <t>https://island.is/en/smitsjukdomar-tolur; https://island.is/en/smitsjukdomar-tolur; https://island.is/en/respiratory-tract-infections; https://island.is/en/smitsjukdomar-tolur; https://island.is/en/smitsjukdomar-tolur</t>
+          <t>https://island.is/en/smitsjukdomar-tolur; https://island.is/en/smitsjukdomar-tolur; https://island.is/en/respiratory-tract-infections; https://island.is/en/smitsjukdomar-tolur; https://island.is/en/smitsjukdomar-tolur; https://atlas.ecdc.europa.eu/public/index.aspx/</t>
         </is>
       </c>
       <c r="BC2" t="inlineStr">
         <is>
-          <t>microsoft_bi; microsoft_bi; microsoft_bi; official_excel; official_excel</t>
+          <t>microsoft_bi; microsoft_bi; microsoft_bi; official_excel; official_excel; official_ecdc_rest_aggregate</t>
         </is>
       </c>
     </row>
@@ -868,7 +853,7 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -899,12 +884,12 @@
       <c r="K3" t="inlineStr"/>
       <c r="L3" t="inlineStr">
         <is>
-          <t>1997-01-01</t>
+          <t>1998-01-01</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>1997-01</t>
+          <t>1998-01</t>
         </is>
       </c>
       <c r="N3" t="n">
@@ -918,94 +903,11 @@
           <t>SER_IS_HISTORY_SMALLPOX_ANNUAL</t>
         </is>
       </c>
-      <c r="V3" t="inlineStr">
-        <is>
-          <t>SER_IS_HISTORY_SMALLPOX_ANNUAL</t>
-        </is>
-      </c>
-      <c r="W3" t="inlineStr">
-        <is>
-          <t>SRC_IS_DOH_HISTORY</t>
-        </is>
-      </c>
-      <c r="X3" t="inlineStr">
-        <is>
-          <t>Bólusótt</t>
-        </is>
-      </c>
-      <c r="Y3" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>national_registry_notifications</t>
-        </is>
-      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>annual</t>
         </is>
       </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>country:IS:national</t>
-        </is>
-      </c>
-      <c r="AD3" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE3" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF3" t="inlineStr">
-        <is>
-          <t>conditional</t>
-        </is>
-      </c>
-      <c r="AG3" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH3" t="inlineStr">
-        <is>
-          <t>historical</t>
-        </is>
-      </c>
-      <c r="AI3" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ3" t="inlineStr">
-        <is>
-          <t>IS_DOH_historical_registry_annual</t>
-        </is>
-      </c>
-      <c r="AK3" t="inlineStr">
-        <is>
-          <t>Iceland historical national-registry annual notifications; published dashes mean not applicable and blank cells remain unknown.</t>
-        </is>
-      </c>
-      <c r="AM3" t="inlineStr">
-        <is>
-          <t>raw</t>
-        </is>
-      </c>
-      <c r="AN3" t="b">
-        <v>1</v>
-      </c>
       <c r="AO3" t="inlineStr">
         <is>
           <t>series_registry</t>
@@ -1013,12 +915,7 @@
       </c>
       <c r="AP3" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ3" t="inlineStr">
-        <is>
-          <t>parity</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS3" t="inlineStr">
@@ -1029,11 +926,6 @@
       <c r="AT3" t="n">
         <v>1</v>
       </c>
-      <c r="AU3" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series.</t>
-        </is>
-      </c>
       <c r="AV3" t="inlineStr">
         <is>
           <t>is_doh_annual</t>
@@ -1056,22 +948,22 @@
       </c>
       <c r="AZ3" t="inlineStr">
         <is>
-          <t>is_doh_annual; is_doh_sti; is_doh_respiratory; is_doh_history; is_doh_legacy_icd</t>
+          <t>is_doh_annual; is_doh_sti; is_doh_respiratory; is_doh_history; is_doh_legacy_icd; ecdc_atlas_annual</t>
         </is>
       </c>
       <c r="BA3" t="inlineStr">
         <is>
-          <t>Iceland Directorate of Health Annual Dashboard; Iceland Directorate of Health STI Dashboard; Iceland Directorate of Health Respiratory Dashboard; Iceland Directorate of Health Historical Registry; Iceland Directorate of Health Legacy ICD Monthly</t>
+          <t>Iceland Directorate of Health Annual Dashboard; Iceland Directorate of Health STI Dashboard; Iceland Directorate of Health Respiratory Dashboard; Iceland Directorate of Health Historical Registry; Iceland Directorate of Health Legacy ICD Monthly; ECDC Surveillance Atlas — Iceland Annual Baseline</t>
         </is>
       </c>
       <c r="BB3" t="inlineStr">
         <is>
-          <t>https://island.is/en/smitsjukdomar-tolur; https://island.is/en/smitsjukdomar-tolur; https://island.is/en/respiratory-tract-infections; https://island.is/en/smitsjukdomar-tolur; https://island.is/en/smitsjukdomar-tolur</t>
+          <t>https://island.is/en/smitsjukdomar-tolur; https://island.is/en/smitsjukdomar-tolur; https://island.is/en/respiratory-tract-infections; https://island.is/en/smitsjukdomar-tolur; https://island.is/en/smitsjukdomar-tolur; https://atlas.ecdc.europa.eu/public/index.aspx/</t>
         </is>
       </c>
       <c r="BC3" t="inlineStr">
         <is>
-          <t>microsoft_bi; microsoft_bi; microsoft_bi; official_excel; official_excel</t>
+          <t>microsoft_bi; microsoft_bi; microsoft_bi; official_excel; official_excel; official_ecdc_rest_aggregate</t>
         </is>
       </c>
     </row>
@@ -1129,12 +1021,12 @@
       <c r="K4" t="inlineStr"/>
       <c r="L4" t="inlineStr">
         <is>
-          <t>1998-01-01</t>
+          <t>1999-01-01</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>1998-01</t>
+          <t>1999-01</t>
         </is>
       </c>
       <c r="N4" t="n">
@@ -1143,11 +1035,6 @@
       <c r="O4" t="n">
         <v>0</v>
       </c>
-      <c r="S4" t="inlineStr">
-        <is>
-          <t>missing_population</t>
-        </is>
-      </c>
       <c r="U4" t="inlineStr">
         <is>
           <t>SER_IS_HISTORY_SMALLPOX_ANNUAL</t>
@@ -1165,12 +1052,7 @@
       </c>
       <c r="AP4" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ4" t="inlineStr">
-        <is>
-          <t>parity</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS4" t="inlineStr">
@@ -1181,11 +1063,6 @@
       <c r="AT4" t="n">
         <v>1</v>
       </c>
-      <c r="AU4" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series.</t>
-        </is>
-      </c>
       <c r="AV4" t="inlineStr">
         <is>
           <t>is_doh_annual</t>
@@ -1208,634 +1085,22 @@
       </c>
       <c r="AZ4" t="inlineStr">
         <is>
-          <t>is_doh_annual; is_doh_sti; is_doh_respiratory; is_doh_history; is_doh_legacy_icd</t>
+          <t>is_doh_annual; is_doh_sti; is_doh_respiratory; is_doh_history; is_doh_legacy_icd; ecdc_atlas_annual</t>
         </is>
       </c>
       <c r="BA4" t="inlineStr">
         <is>
-          <t>Iceland Directorate of Health Annual Dashboard; Iceland Directorate of Health STI Dashboard; Iceland Directorate of Health Respiratory Dashboard; Iceland Directorate of Health Historical Registry; Iceland Directorate of Health Legacy ICD Monthly</t>
+          <t>Iceland Directorate of Health Annual Dashboard; Iceland Directorate of Health STI Dashboard; Iceland Directorate of Health Respiratory Dashboard; Iceland Directorate of Health Historical Registry; Iceland Directorate of Health Legacy ICD Monthly; ECDC Surveillance Atlas — Iceland Annual Baseline</t>
         </is>
       </c>
       <c r="BB4" t="inlineStr">
         <is>
-          <t>https://island.is/en/smitsjukdomar-tolur; https://island.is/en/smitsjukdomar-tolur; https://island.is/en/respiratory-tract-infections; https://island.is/en/smitsjukdomar-tolur; https://island.is/en/smitsjukdomar-tolur</t>
+          <t>https://island.is/en/smitsjukdomar-tolur; https://island.is/en/smitsjukdomar-tolur; https://island.is/en/respiratory-tract-infections; https://island.is/en/smitsjukdomar-tolur; https://island.is/en/smitsjukdomar-tolur; https://atlas.ecdc.europa.eu/public/index.aspx/</t>
         </is>
       </c>
       <c r="BC4" t="inlineStr">
         <is>
-          <t>microsoft_bi; microsoft_bi; microsoft_bi; official_excel; official_excel</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>disease</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>D064</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>smallpox</t>
-        </is>
-      </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>Smallpox</t>
-        </is>
-      </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>source_series_observation</t>
-        </is>
-      </c>
-      <c r="F5" t="inlineStr">
-        <is>
-          <t>IS</t>
-        </is>
-      </c>
-      <c r="G5" t="inlineStr">
-        <is>
-          <t>Iceland</t>
-        </is>
-      </c>
-      <c r="H5" t="inlineStr">
-        <is>
-          <t>D064</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>Smallpox</t>
-        </is>
-      </c>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>天花</t>
-        </is>
-      </c>
-      <c r="K5" t="inlineStr"/>
-      <c r="L5" t="inlineStr">
-        <is>
-          <t>1998-01-01</t>
-        </is>
-      </c>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>1998-01</t>
-        </is>
-      </c>
-      <c r="N5" t="n">
-        <v>0</v>
-      </c>
-      <c r="O5" t="n">
-        <v>0</v>
-      </c>
-      <c r="U5" t="inlineStr">
-        <is>
-          <t>SER_IS_HISTORY_SMALLPOX_ANNUAL</t>
-        </is>
-      </c>
-      <c r="V5" t="inlineStr">
-        <is>
-          <t>SER_IS_HISTORY_SMALLPOX_ANNUAL</t>
-        </is>
-      </c>
-      <c r="W5" t="inlineStr">
-        <is>
-          <t>SRC_IS_DOH_HISTORY</t>
-        </is>
-      </c>
-      <c r="X5" t="inlineStr">
-        <is>
-          <t>Bólusótt</t>
-        </is>
-      </c>
-      <c r="Y5" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>national_registry_notifications</t>
-        </is>
-      </c>
-      <c r="AA5" t="inlineStr">
-        <is>
-          <t>annual</t>
-        </is>
-      </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>country:IS:national</t>
-        </is>
-      </c>
-      <c r="AD5" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE5" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF5" t="inlineStr">
-        <is>
-          <t>conditional</t>
-        </is>
-      </c>
-      <c r="AG5" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH5" t="inlineStr">
-        <is>
-          <t>historical</t>
-        </is>
-      </c>
-      <c r="AI5" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ5" t="inlineStr">
-        <is>
-          <t>IS_DOH_historical_registry_annual</t>
-        </is>
-      </c>
-      <c r="AK5" t="inlineStr">
-        <is>
-          <t>Iceland historical national-registry annual notifications; published dashes mean not applicable and blank cells remain unknown.</t>
-        </is>
-      </c>
-      <c r="AM5" t="inlineStr">
-        <is>
-          <t>raw</t>
-        </is>
-      </c>
-      <c r="AN5" t="b">
-        <v>1</v>
-      </c>
-      <c r="AO5" t="inlineStr">
-        <is>
-          <t>series_registry</t>
-        </is>
-      </c>
-      <c r="AP5" t="inlineStr">
-        <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ5" t="inlineStr">
-        <is>
-          <t>parity</t>
-        </is>
-      </c>
-      <c r="AS5" t="inlineStr">
-        <is>
-          <t>SER_IS_HISTORY_SMALLPOX_ANNUAL</t>
-        </is>
-      </c>
-      <c r="AT5" t="n">
-        <v>1</v>
-      </c>
-      <c r="AU5" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series.</t>
-        </is>
-      </c>
-      <c r="AV5" t="inlineStr">
-        <is>
-          <t>is_doh_annual</t>
-        </is>
-      </c>
-      <c r="AW5" t="inlineStr">
-        <is>
-          <t>Iceland Directorate of Health Annual Dashboard</t>
-        </is>
-      </c>
-      <c r="AX5" t="inlineStr">
-        <is>
-          <t>https://island.is/en/smitsjukdomar-tolur</t>
-        </is>
-      </c>
-      <c r="AY5" t="inlineStr">
-        <is>
-          <t>microsoft_bi</t>
-        </is>
-      </c>
-      <c r="AZ5" t="inlineStr">
-        <is>
-          <t>is_doh_annual; is_doh_sti; is_doh_respiratory; is_doh_history; is_doh_legacy_icd</t>
-        </is>
-      </c>
-      <c r="BA5" t="inlineStr">
-        <is>
-          <t>Iceland Directorate of Health Annual Dashboard; Iceland Directorate of Health STI Dashboard; Iceland Directorate of Health Respiratory Dashboard; Iceland Directorate of Health Historical Registry; Iceland Directorate of Health Legacy ICD Monthly</t>
-        </is>
-      </c>
-      <c r="BB5" t="inlineStr">
-        <is>
-          <t>https://island.is/en/smitsjukdomar-tolur; https://island.is/en/smitsjukdomar-tolur; https://island.is/en/respiratory-tract-infections; https://island.is/en/smitsjukdomar-tolur; https://island.is/en/smitsjukdomar-tolur</t>
-        </is>
-      </c>
-      <c r="BC5" t="inlineStr">
-        <is>
-          <t>microsoft_bi; microsoft_bi; microsoft_bi; official_excel; official_excel</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>disease</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>D064</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>smallpox</t>
-        </is>
-      </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>Smallpox</t>
-        </is>
-      </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>public_projection</t>
-        </is>
-      </c>
-      <c r="F6" t="inlineStr">
-        <is>
-          <t>IS</t>
-        </is>
-      </c>
-      <c r="G6" t="inlineStr">
-        <is>
-          <t>Iceland</t>
-        </is>
-      </c>
-      <c r="H6" t="inlineStr">
-        <is>
-          <t>D064</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>Smallpox</t>
-        </is>
-      </c>
-      <c r="J6" t="inlineStr">
-        <is>
-          <t>天花</t>
-        </is>
-      </c>
-      <c r="K6" t="inlineStr"/>
-      <c r="L6" t="inlineStr">
-        <is>
-          <t>1999-01-01</t>
-        </is>
-      </c>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>1999-01</t>
-        </is>
-      </c>
-      <c r="N6" t="n">
-        <v>0</v>
-      </c>
-      <c r="O6" t="n">
-        <v>0</v>
-      </c>
-      <c r="S6" t="inlineStr">
-        <is>
-          <t>missing_population</t>
-        </is>
-      </c>
-      <c r="U6" t="inlineStr">
-        <is>
-          <t>SER_IS_HISTORY_SMALLPOX_ANNUAL</t>
-        </is>
-      </c>
-      <c r="AA6" t="inlineStr">
-        <is>
-          <t>annual</t>
-        </is>
-      </c>
-      <c r="AO6" t="inlineStr">
-        <is>
-          <t>series_registry</t>
-        </is>
-      </c>
-      <c r="AP6" t="inlineStr">
-        <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ6" t="inlineStr">
-        <is>
-          <t>parity</t>
-        </is>
-      </c>
-      <c r="AS6" t="inlineStr">
-        <is>
-          <t>SER_IS_HISTORY_SMALLPOX_ANNUAL</t>
-        </is>
-      </c>
-      <c r="AT6" t="n">
-        <v>1</v>
-      </c>
-      <c r="AU6" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series.</t>
-        </is>
-      </c>
-      <c r="AV6" t="inlineStr">
-        <is>
-          <t>is_doh_annual</t>
-        </is>
-      </c>
-      <c r="AW6" t="inlineStr">
-        <is>
-          <t>Iceland Directorate of Health Annual Dashboard</t>
-        </is>
-      </c>
-      <c r="AX6" t="inlineStr">
-        <is>
-          <t>https://island.is/en/smitsjukdomar-tolur</t>
-        </is>
-      </c>
-      <c r="AY6" t="inlineStr">
-        <is>
-          <t>microsoft_bi</t>
-        </is>
-      </c>
-      <c r="AZ6" t="inlineStr">
-        <is>
-          <t>is_doh_annual; is_doh_sti; is_doh_respiratory; is_doh_history; is_doh_legacy_icd</t>
-        </is>
-      </c>
-      <c r="BA6" t="inlineStr">
-        <is>
-          <t>Iceland Directorate of Health Annual Dashboard; Iceland Directorate of Health STI Dashboard; Iceland Directorate of Health Respiratory Dashboard; Iceland Directorate of Health Historical Registry; Iceland Directorate of Health Legacy ICD Monthly</t>
-        </is>
-      </c>
-      <c r="BB6" t="inlineStr">
-        <is>
-          <t>https://island.is/en/smitsjukdomar-tolur; https://island.is/en/smitsjukdomar-tolur; https://island.is/en/respiratory-tract-infections; https://island.is/en/smitsjukdomar-tolur; https://island.is/en/smitsjukdomar-tolur</t>
-        </is>
-      </c>
-      <c r="BC6" t="inlineStr">
-        <is>
-          <t>microsoft_bi; microsoft_bi; microsoft_bi; official_excel; official_excel</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>disease</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>D064</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>smallpox</t>
-        </is>
-      </c>
-      <c r="D7" t="inlineStr">
-        <is>
-          <t>Smallpox</t>
-        </is>
-      </c>
-      <c r="E7" t="inlineStr">
-        <is>
-          <t>source_series_observation</t>
-        </is>
-      </c>
-      <c r="F7" t="inlineStr">
-        <is>
-          <t>IS</t>
-        </is>
-      </c>
-      <c r="G7" t="inlineStr">
-        <is>
-          <t>Iceland</t>
-        </is>
-      </c>
-      <c r="H7" t="inlineStr">
-        <is>
-          <t>D064</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>Smallpox</t>
-        </is>
-      </c>
-      <c r="J7" t="inlineStr">
-        <is>
-          <t>天花</t>
-        </is>
-      </c>
-      <c r="K7" t="inlineStr"/>
-      <c r="L7" t="inlineStr">
-        <is>
-          <t>1999-01-01</t>
-        </is>
-      </c>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>1999-01</t>
-        </is>
-      </c>
-      <c r="N7" t="n">
-        <v>0</v>
-      </c>
-      <c r="O7" t="n">
-        <v>0</v>
-      </c>
-      <c r="U7" t="inlineStr">
-        <is>
-          <t>SER_IS_HISTORY_SMALLPOX_ANNUAL</t>
-        </is>
-      </c>
-      <c r="V7" t="inlineStr">
-        <is>
-          <t>SER_IS_HISTORY_SMALLPOX_ANNUAL</t>
-        </is>
-      </c>
-      <c r="W7" t="inlineStr">
-        <is>
-          <t>SRC_IS_DOH_HISTORY</t>
-        </is>
-      </c>
-      <c r="X7" t="inlineStr">
-        <is>
-          <t>Bólusótt</t>
-        </is>
-      </c>
-      <c r="Y7" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z7" t="inlineStr">
-        <is>
-          <t>national_registry_notifications</t>
-        </is>
-      </c>
-      <c r="AA7" t="inlineStr">
-        <is>
-          <t>annual</t>
-        </is>
-      </c>
-      <c r="AB7" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC7" t="inlineStr">
-        <is>
-          <t>country:IS:national</t>
-        </is>
-      </c>
-      <c r="AD7" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE7" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF7" t="inlineStr">
-        <is>
-          <t>conditional</t>
-        </is>
-      </c>
-      <c r="AG7" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH7" t="inlineStr">
-        <is>
-          <t>historical</t>
-        </is>
-      </c>
-      <c r="AI7" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ7" t="inlineStr">
-        <is>
-          <t>IS_DOH_historical_registry_annual</t>
-        </is>
-      </c>
-      <c r="AK7" t="inlineStr">
-        <is>
-          <t>Iceland historical national-registry annual notifications; published dashes mean not applicable and blank cells remain unknown.</t>
-        </is>
-      </c>
-      <c r="AM7" t="inlineStr">
-        <is>
-          <t>raw</t>
-        </is>
-      </c>
-      <c r="AN7" t="b">
-        <v>1</v>
-      </c>
-      <c r="AO7" t="inlineStr">
-        <is>
-          <t>series_registry</t>
-        </is>
-      </c>
-      <c r="AP7" t="inlineStr">
-        <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ7" t="inlineStr">
-        <is>
-          <t>parity</t>
-        </is>
-      </c>
-      <c r="AS7" t="inlineStr">
-        <is>
-          <t>SER_IS_HISTORY_SMALLPOX_ANNUAL</t>
-        </is>
-      </c>
-      <c r="AT7" t="n">
-        <v>1</v>
-      </c>
-      <c r="AU7" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series.</t>
-        </is>
-      </c>
-      <c r="AV7" t="inlineStr">
-        <is>
-          <t>is_doh_annual</t>
-        </is>
-      </c>
-      <c r="AW7" t="inlineStr">
-        <is>
-          <t>Iceland Directorate of Health Annual Dashboard</t>
-        </is>
-      </c>
-      <c r="AX7" t="inlineStr">
-        <is>
-          <t>https://island.is/en/smitsjukdomar-tolur</t>
-        </is>
-      </c>
-      <c r="AY7" t="inlineStr">
-        <is>
-          <t>microsoft_bi</t>
-        </is>
-      </c>
-      <c r="AZ7" t="inlineStr">
-        <is>
-          <t>is_doh_annual; is_doh_sti; is_doh_respiratory; is_doh_history; is_doh_legacy_icd</t>
-        </is>
-      </c>
-      <c r="BA7" t="inlineStr">
-        <is>
-          <t>Iceland Directorate of Health Annual Dashboard; Iceland Directorate of Health STI Dashboard; Iceland Directorate of Health Respiratory Dashboard; Iceland Directorate of Health Historical Registry; Iceland Directorate of Health Legacy ICD Monthly</t>
-        </is>
-      </c>
-      <c r="BB7" t="inlineStr">
-        <is>
-          <t>https://island.is/en/smitsjukdomar-tolur; https://island.is/en/smitsjukdomar-tolur; https://island.is/en/respiratory-tract-infections; https://island.is/en/smitsjukdomar-tolur; https://island.is/en/smitsjukdomar-tolur</t>
-        </is>
-      </c>
-      <c r="BC7" t="inlineStr">
-        <is>
-          <t>microsoft_bi; microsoft_bi; microsoft_bi; official_excel; official_excel</t>
+          <t>microsoft_bi; microsoft_bi; microsoft_bi; official_excel; official_excel; official_ecdc_rest_aggregate</t>
         </is>
       </c>
     </row>
@@ -1965,7 +1230,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
     </row>
     <row r="11">
@@ -1985,7 +1250,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="13">
@@ -1995,7 +1260,7 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="14">

--- a/diseases/d064/1995-1999.xlsx
+++ b/diseases/d064/1995-1999.xlsx
@@ -761,6 +761,11 @@
       <c r="O2" t="n">
         <v>0</v>
       </c>
+      <c r="S2" t="inlineStr">
+        <is>
+          <t>missing_population</t>
+        </is>
+      </c>
       <c r="U2" t="inlineStr">
         <is>
           <t>SER_IS_HISTORY_SMALLPOX_ANNUAL</t>
@@ -778,7 +783,12 @@
       </c>
       <c r="AP2" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ2" t="inlineStr">
+        <is>
+          <t>parity</t>
         </is>
       </c>
       <c r="AS2" t="inlineStr">
@@ -789,6 +799,11 @@
       <c r="AT2" t="n">
         <v>1</v>
       </c>
+      <c r="AU2" t="inlineStr">
+        <is>
+          <t>The public curve is read directly from one registered source series.</t>
+        </is>
+      </c>
       <c r="AV2" t="inlineStr">
         <is>
           <t>is_doh_annual</t>
@@ -811,22 +826,22 @@
       </c>
       <c r="AZ2" t="inlineStr">
         <is>
-          <t>is_doh_annual; is_doh_sti; is_doh_respiratory; is_doh_history; is_doh_legacy_icd; ecdc_atlas_annual</t>
+          <t>is_doh_annual; is_doh_sti; is_doh_respiratory; is_doh_history; is_doh_legacy_icd</t>
         </is>
       </c>
       <c r="BA2" t="inlineStr">
         <is>
-          <t>Iceland Directorate of Health Annual Dashboard; Iceland Directorate of Health STI Dashboard; Iceland Directorate of Health Respiratory Dashboard; Iceland Directorate of Health Historical Registry; Iceland Directorate of Health Legacy ICD Monthly; ECDC Surveillance Atlas — Iceland Annual Baseline</t>
+          <t>Iceland Directorate of Health Annual Dashboard; Iceland Directorate of Health STI Dashboard; Iceland Directorate of Health Respiratory Dashboard; Iceland Directorate of Health Historical Registry; Iceland Directorate of Health Legacy ICD Monthly</t>
         </is>
       </c>
       <c r="BB2" t="inlineStr">
         <is>
-          <t>https://island.is/en/smitsjukdomar-tolur; https://island.is/en/smitsjukdomar-tolur; https://island.is/en/respiratory-tract-infections; https://island.is/en/smitsjukdomar-tolur; https://island.is/en/smitsjukdomar-tolur; https://atlas.ecdc.europa.eu/public/index.aspx/</t>
+          <t>https://island.is/en/smitsjukdomar-tolur; https://island.is/en/smitsjukdomar-tolur; https://island.is/en/respiratory-tract-infections; https://island.is/en/smitsjukdomar-tolur; https://island.is/en/smitsjukdomar-tolur</t>
         </is>
       </c>
       <c r="BC2" t="inlineStr">
         <is>
-          <t>microsoft_bi; microsoft_bi; microsoft_bi; official_excel; official_excel; official_ecdc_rest_aggregate</t>
+          <t>microsoft_bi; microsoft_bi; microsoft_bi; official_excel; official_excel</t>
         </is>
       </c>
     </row>
@@ -853,7 +868,7 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -884,12 +899,12 @@
       <c r="K3" t="inlineStr"/>
       <c r="L3" t="inlineStr">
         <is>
-          <t>1998-01-01</t>
+          <t>1997-01-01</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>1998-01</t>
+          <t>1997-01</t>
         </is>
       </c>
       <c r="N3" t="n">
@@ -903,11 +918,94 @@
           <t>SER_IS_HISTORY_SMALLPOX_ANNUAL</t>
         </is>
       </c>
+      <c r="V3" t="inlineStr">
+        <is>
+          <t>SER_IS_HISTORY_SMALLPOX_ANNUAL</t>
+        </is>
+      </c>
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>SRC_IS_DOH_HISTORY</t>
+        </is>
+      </c>
+      <c r="X3" t="inlineStr">
+        <is>
+          <t>Bólusótt</t>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z3" t="inlineStr">
+        <is>
+          <t>national_registry_notifications</t>
+        </is>
+      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>annual</t>
         </is>
       </c>
+      <c r="AB3" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>country:IS:national</t>
+        </is>
+      </c>
+      <c r="AD3" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE3" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF3" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG3" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH3" t="inlineStr">
+        <is>
+          <t>historical</t>
+        </is>
+      </c>
+      <c r="AI3" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ3" t="inlineStr">
+        <is>
+          <t>IS_DOH_historical_registry_annual</t>
+        </is>
+      </c>
+      <c r="AK3" t="inlineStr">
+        <is>
+          <t>Iceland historical national-registry annual notifications; published dashes mean not applicable and blank cells remain unknown.</t>
+        </is>
+      </c>
+      <c r="AM3" t="inlineStr">
+        <is>
+          <t>raw</t>
+        </is>
+      </c>
+      <c r="AN3" t="b">
+        <v>1</v>
+      </c>
       <c r="AO3" t="inlineStr">
         <is>
           <t>series_registry</t>
@@ -915,7 +1013,12 @@
       </c>
       <c r="AP3" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ3" t="inlineStr">
+        <is>
+          <t>parity</t>
         </is>
       </c>
       <c r="AS3" t="inlineStr">
@@ -926,6 +1029,11 @@
       <c r="AT3" t="n">
         <v>1</v>
       </c>
+      <c r="AU3" t="inlineStr">
+        <is>
+          <t>The public curve is read directly from one registered source series.</t>
+        </is>
+      </c>
       <c r="AV3" t="inlineStr">
         <is>
           <t>is_doh_annual</t>
@@ -948,22 +1056,22 @@
       </c>
       <c r="AZ3" t="inlineStr">
         <is>
-          <t>is_doh_annual; is_doh_sti; is_doh_respiratory; is_doh_history; is_doh_legacy_icd; ecdc_atlas_annual</t>
+          <t>is_doh_annual; is_doh_sti; is_doh_respiratory; is_doh_history; is_doh_legacy_icd</t>
         </is>
       </c>
       <c r="BA3" t="inlineStr">
         <is>
-          <t>Iceland Directorate of Health Annual Dashboard; Iceland Directorate of Health STI Dashboard; Iceland Directorate of Health Respiratory Dashboard; Iceland Directorate of Health Historical Registry; Iceland Directorate of Health Legacy ICD Monthly; ECDC Surveillance Atlas — Iceland Annual Baseline</t>
+          <t>Iceland Directorate of Health Annual Dashboard; Iceland Directorate of Health STI Dashboard; Iceland Directorate of Health Respiratory Dashboard; Iceland Directorate of Health Historical Registry; Iceland Directorate of Health Legacy ICD Monthly</t>
         </is>
       </c>
       <c r="BB3" t="inlineStr">
         <is>
-          <t>https://island.is/en/smitsjukdomar-tolur; https://island.is/en/smitsjukdomar-tolur; https://island.is/en/respiratory-tract-infections; https://island.is/en/smitsjukdomar-tolur; https://island.is/en/smitsjukdomar-tolur; https://atlas.ecdc.europa.eu/public/index.aspx/</t>
+          <t>https://island.is/en/smitsjukdomar-tolur; https://island.is/en/smitsjukdomar-tolur; https://island.is/en/respiratory-tract-infections; https://island.is/en/smitsjukdomar-tolur; https://island.is/en/smitsjukdomar-tolur</t>
         </is>
       </c>
       <c r="BC3" t="inlineStr">
         <is>
-          <t>microsoft_bi; microsoft_bi; microsoft_bi; official_excel; official_excel; official_ecdc_rest_aggregate</t>
+          <t>microsoft_bi; microsoft_bi; microsoft_bi; official_excel; official_excel</t>
         </is>
       </c>
     </row>
@@ -1021,12 +1129,12 @@
       <c r="K4" t="inlineStr"/>
       <c r="L4" t="inlineStr">
         <is>
-          <t>1999-01-01</t>
+          <t>1998-01-01</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>1999-01</t>
+          <t>1998-01</t>
         </is>
       </c>
       <c r="N4" t="n">
@@ -1035,6 +1143,11 @@
       <c r="O4" t="n">
         <v>0</v>
       </c>
+      <c r="S4" t="inlineStr">
+        <is>
+          <t>missing_population</t>
+        </is>
+      </c>
       <c r="U4" t="inlineStr">
         <is>
           <t>SER_IS_HISTORY_SMALLPOX_ANNUAL</t>
@@ -1052,7 +1165,12 @@
       </c>
       <c r="AP4" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ4" t="inlineStr">
+        <is>
+          <t>parity</t>
         </is>
       </c>
       <c r="AS4" t="inlineStr">
@@ -1063,6 +1181,11 @@
       <c r="AT4" t="n">
         <v>1</v>
       </c>
+      <c r="AU4" t="inlineStr">
+        <is>
+          <t>The public curve is read directly from one registered source series.</t>
+        </is>
+      </c>
       <c r="AV4" t="inlineStr">
         <is>
           <t>is_doh_annual</t>
@@ -1085,22 +1208,634 @@
       </c>
       <c r="AZ4" t="inlineStr">
         <is>
-          <t>is_doh_annual; is_doh_sti; is_doh_respiratory; is_doh_history; is_doh_legacy_icd; ecdc_atlas_annual</t>
+          <t>is_doh_annual; is_doh_sti; is_doh_respiratory; is_doh_history; is_doh_legacy_icd</t>
         </is>
       </c>
       <c r="BA4" t="inlineStr">
         <is>
-          <t>Iceland Directorate of Health Annual Dashboard; Iceland Directorate of Health STI Dashboard; Iceland Directorate of Health Respiratory Dashboard; Iceland Directorate of Health Historical Registry; Iceland Directorate of Health Legacy ICD Monthly; ECDC Surveillance Atlas — Iceland Annual Baseline</t>
+          <t>Iceland Directorate of Health Annual Dashboard; Iceland Directorate of Health STI Dashboard; Iceland Directorate of Health Respiratory Dashboard; Iceland Directorate of Health Historical Registry; Iceland Directorate of Health Legacy ICD Monthly</t>
         </is>
       </c>
       <c r="BB4" t="inlineStr">
         <is>
-          <t>https://island.is/en/smitsjukdomar-tolur; https://island.is/en/smitsjukdomar-tolur; https://island.is/en/respiratory-tract-infections; https://island.is/en/smitsjukdomar-tolur; https://island.is/en/smitsjukdomar-tolur; https://atlas.ecdc.europa.eu/public/index.aspx/</t>
+          <t>https://island.is/en/smitsjukdomar-tolur; https://island.is/en/smitsjukdomar-tolur; https://island.is/en/respiratory-tract-infections; https://island.is/en/smitsjukdomar-tolur; https://island.is/en/smitsjukdomar-tolur</t>
         </is>
       </c>
       <c r="BC4" t="inlineStr">
         <is>
-          <t>microsoft_bi; microsoft_bi; microsoft_bi; official_excel; official_excel; official_ecdc_rest_aggregate</t>
+          <t>microsoft_bi; microsoft_bi; microsoft_bi; official_excel; official_excel</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>D064</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>smallpox</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>Smallpox</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>source_series_observation</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>IS</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Iceland</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>D064</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>Smallpox</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>天花</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr"/>
+      <c r="L5" t="inlineStr">
+        <is>
+          <t>1998-01-01</t>
+        </is>
+      </c>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>1998-01</t>
+        </is>
+      </c>
+      <c r="N5" t="n">
+        <v>0</v>
+      </c>
+      <c r="O5" t="n">
+        <v>0</v>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>SER_IS_HISTORY_SMALLPOX_ANNUAL</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>SER_IS_HISTORY_SMALLPOX_ANNUAL</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>SRC_IS_DOH_HISTORY</t>
+        </is>
+      </c>
+      <c r="X5" t="inlineStr">
+        <is>
+          <t>Bólusótt</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z5" t="inlineStr">
+        <is>
+          <t>national_registry_notifications</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>annual</t>
+        </is>
+      </c>
+      <c r="AB5" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>country:IS:national</t>
+        </is>
+      </c>
+      <c r="AD5" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE5" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF5" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG5" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH5" t="inlineStr">
+        <is>
+          <t>historical</t>
+        </is>
+      </c>
+      <c r="AI5" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ5" t="inlineStr">
+        <is>
+          <t>IS_DOH_historical_registry_annual</t>
+        </is>
+      </c>
+      <c r="AK5" t="inlineStr">
+        <is>
+          <t>Iceland historical national-registry annual notifications; published dashes mean not applicable and blank cells remain unknown.</t>
+        </is>
+      </c>
+      <c r="AM5" t="inlineStr">
+        <is>
+          <t>raw</t>
+        </is>
+      </c>
+      <c r="AN5" t="b">
+        <v>1</v>
+      </c>
+      <c r="AO5" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP5" t="inlineStr">
+        <is>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ5" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS5" t="inlineStr">
+        <is>
+          <t>SER_IS_HISTORY_SMALLPOX_ANNUAL</t>
+        </is>
+      </c>
+      <c r="AT5" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU5" t="inlineStr">
+        <is>
+          <t>The public curve is read directly from one registered source series.</t>
+        </is>
+      </c>
+      <c r="AV5" t="inlineStr">
+        <is>
+          <t>is_doh_annual</t>
+        </is>
+      </c>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>Iceland Directorate of Health Annual Dashboard</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>https://island.is/en/smitsjukdomar-tolur</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr">
+        <is>
+          <t>microsoft_bi</t>
+        </is>
+      </c>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>is_doh_annual; is_doh_sti; is_doh_respiratory; is_doh_history; is_doh_legacy_icd</t>
+        </is>
+      </c>
+      <c r="BA5" t="inlineStr">
+        <is>
+          <t>Iceland Directorate of Health Annual Dashboard; Iceland Directorate of Health STI Dashboard; Iceland Directorate of Health Respiratory Dashboard; Iceland Directorate of Health Historical Registry; Iceland Directorate of Health Legacy ICD Monthly</t>
+        </is>
+      </c>
+      <c r="BB5" t="inlineStr">
+        <is>
+          <t>https://island.is/en/smitsjukdomar-tolur; https://island.is/en/smitsjukdomar-tolur; https://island.is/en/respiratory-tract-infections; https://island.is/en/smitsjukdomar-tolur; https://island.is/en/smitsjukdomar-tolur</t>
+        </is>
+      </c>
+      <c r="BC5" t="inlineStr">
+        <is>
+          <t>microsoft_bi; microsoft_bi; microsoft_bi; official_excel; official_excel</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>D064</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>smallpox</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>Smallpox</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>IS</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Iceland</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>D064</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>Smallpox</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>天花</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr"/>
+      <c r="L6" t="inlineStr">
+        <is>
+          <t>1999-01-01</t>
+        </is>
+      </c>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>1999-01</t>
+        </is>
+      </c>
+      <c r="N6" t="n">
+        <v>0</v>
+      </c>
+      <c r="O6" t="n">
+        <v>0</v>
+      </c>
+      <c r="S6" t="inlineStr">
+        <is>
+          <t>missing_population</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>SER_IS_HISTORY_SMALLPOX_ANNUAL</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>annual</t>
+        </is>
+      </c>
+      <c r="AO6" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP6" t="inlineStr">
+        <is>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ6" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS6" t="inlineStr">
+        <is>
+          <t>SER_IS_HISTORY_SMALLPOX_ANNUAL</t>
+        </is>
+      </c>
+      <c r="AT6" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU6" t="inlineStr">
+        <is>
+          <t>The public curve is read directly from one registered source series.</t>
+        </is>
+      </c>
+      <c r="AV6" t="inlineStr">
+        <is>
+          <t>is_doh_annual</t>
+        </is>
+      </c>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>Iceland Directorate of Health Annual Dashboard</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>https://island.is/en/smitsjukdomar-tolur</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr">
+        <is>
+          <t>microsoft_bi</t>
+        </is>
+      </c>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>is_doh_annual; is_doh_sti; is_doh_respiratory; is_doh_history; is_doh_legacy_icd</t>
+        </is>
+      </c>
+      <c r="BA6" t="inlineStr">
+        <is>
+          <t>Iceland Directorate of Health Annual Dashboard; Iceland Directorate of Health STI Dashboard; Iceland Directorate of Health Respiratory Dashboard; Iceland Directorate of Health Historical Registry; Iceland Directorate of Health Legacy ICD Monthly</t>
+        </is>
+      </c>
+      <c r="BB6" t="inlineStr">
+        <is>
+          <t>https://island.is/en/smitsjukdomar-tolur; https://island.is/en/smitsjukdomar-tolur; https://island.is/en/respiratory-tract-infections; https://island.is/en/smitsjukdomar-tolur; https://island.is/en/smitsjukdomar-tolur</t>
+        </is>
+      </c>
+      <c r="BC6" t="inlineStr">
+        <is>
+          <t>microsoft_bi; microsoft_bi; microsoft_bi; official_excel; official_excel</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>D064</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>smallpox</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>Smallpox</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>source_series_observation</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>IS</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Iceland</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>D064</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>Smallpox</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>天花</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr"/>
+      <c r="L7" t="inlineStr">
+        <is>
+          <t>1999-01-01</t>
+        </is>
+      </c>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>1999-01</t>
+        </is>
+      </c>
+      <c r="N7" t="n">
+        <v>0</v>
+      </c>
+      <c r="O7" t="n">
+        <v>0</v>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>SER_IS_HISTORY_SMALLPOX_ANNUAL</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>SER_IS_HISTORY_SMALLPOX_ANNUAL</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>SRC_IS_DOH_HISTORY</t>
+        </is>
+      </c>
+      <c r="X7" t="inlineStr">
+        <is>
+          <t>Bólusótt</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z7" t="inlineStr">
+        <is>
+          <t>national_registry_notifications</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>annual</t>
+        </is>
+      </c>
+      <c r="AB7" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>country:IS:national</t>
+        </is>
+      </c>
+      <c r="AD7" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE7" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF7" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG7" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH7" t="inlineStr">
+        <is>
+          <t>historical</t>
+        </is>
+      </c>
+      <c r="AI7" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ7" t="inlineStr">
+        <is>
+          <t>IS_DOH_historical_registry_annual</t>
+        </is>
+      </c>
+      <c r="AK7" t="inlineStr">
+        <is>
+          <t>Iceland historical national-registry annual notifications; published dashes mean not applicable and blank cells remain unknown.</t>
+        </is>
+      </c>
+      <c r="AM7" t="inlineStr">
+        <is>
+          <t>raw</t>
+        </is>
+      </c>
+      <c r="AN7" t="b">
+        <v>1</v>
+      </c>
+      <c r="AO7" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP7" t="inlineStr">
+        <is>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ7" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS7" t="inlineStr">
+        <is>
+          <t>SER_IS_HISTORY_SMALLPOX_ANNUAL</t>
+        </is>
+      </c>
+      <c r="AT7" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU7" t="inlineStr">
+        <is>
+          <t>The public curve is read directly from one registered source series.</t>
+        </is>
+      </c>
+      <c r="AV7" t="inlineStr">
+        <is>
+          <t>is_doh_annual</t>
+        </is>
+      </c>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>Iceland Directorate of Health Annual Dashboard</t>
+        </is>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>https://island.is/en/smitsjukdomar-tolur</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr">
+        <is>
+          <t>microsoft_bi</t>
+        </is>
+      </c>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>is_doh_annual; is_doh_sti; is_doh_respiratory; is_doh_history; is_doh_legacy_icd</t>
+        </is>
+      </c>
+      <c r="BA7" t="inlineStr">
+        <is>
+          <t>Iceland Directorate of Health Annual Dashboard; Iceland Directorate of Health STI Dashboard; Iceland Directorate of Health Respiratory Dashboard; Iceland Directorate of Health Historical Registry; Iceland Directorate of Health Legacy ICD Monthly</t>
+        </is>
+      </c>
+      <c r="BB7" t="inlineStr">
+        <is>
+          <t>https://island.is/en/smitsjukdomar-tolur; https://island.is/en/smitsjukdomar-tolur; https://island.is/en/respiratory-tract-infections; https://island.is/en/smitsjukdomar-tolur; https://island.is/en/smitsjukdomar-tolur</t>
+        </is>
+      </c>
+      <c r="BC7" t="inlineStr">
+        <is>
+          <t>microsoft_bi; microsoft_bi; microsoft_bi; official_excel; official_excel</t>
         </is>
       </c>
     </row>
@@ -1230,7 +1965,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
     </row>
     <row r="11">
@@ -1250,7 +1985,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
     </row>
     <row r="13">
@@ -1260,7 +1995,7 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="14">
